--- a/data/trans_dic/IP07_C11_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C11_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen muchos o muchísimos problemas para dormir, percibido por el menor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,11</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,64; 31,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1,31; 15,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,37%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>1,51; 10,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1,03; 9,22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1,94; 9,24</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,71</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1,69; 16,92</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1,05; 7,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>10,23%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>4,42; 19,38</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,9; 14,34</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4,91; 14,49</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 7,0</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 10,74</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3,65; 7,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.01232756428152584</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.103412949009192</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.05043046166835899</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>586</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3535</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4121</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.01642389433142033</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.0131072138463549</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3379</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>561; 10826</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1071; 12453</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.0711028486738898</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.3167267620982921</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1524026413583665</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.04844010588814954</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.03526479322165819</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.04370268669073933</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4937</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6955</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.01512407840671275</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.01028082774261073</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.01936079121988933</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>1542; 11093</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>588; 5278</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3081; 14709</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1088404750589959</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.09223814574761809</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.09242422346585699</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.005513713584695117</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.06759622336084575</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.03233696493165795</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3334</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>3691</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.01691264223828434</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.01051331658637429</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0; 1760</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>834; 8346</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1200; 8292</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.02714212842188317</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1692200660787225</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.07264145608812936</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1023306905821624</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.06936235503633552</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.08569357404140264</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>5712</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3944</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9656</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.04415431968531754</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.01902825531493444</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.04911700674343775</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>2465; 10821</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>1082; 8154</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>5535; 16333</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1938486256159479</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1433867618774878</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.1449403179018326</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.04291972559507507</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.0649365817223452</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.05222136713447853</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>11593</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>12831</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24423</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.02334315025834651</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.03687671746223254</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.03645664564330427</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>6305; 18901</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>7286; 21217</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17050; 36334</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.06997729522484769</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1073820666162268</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.077689330318472</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir, percibido por el menor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>586</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3535</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>4121</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>561</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>3379</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>10826</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>12453</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>4937</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>6955</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1542</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>588</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>3081</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>11093</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>5278</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>14709</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>357</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>3334</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>3691</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>834</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>8346</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>8292</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>5712</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>3944</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>9656</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>2465</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>5535</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>10821</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>8154</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>16333</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>11593</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>12831</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>24423</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>6305</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>7286</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>17050</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>18901</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>21217</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>36334</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>